--- a/Result/checksun_type/機器人.xlsx
+++ b/Result/checksun_type/機器人.xlsx
@@ -641,62 +641,62 @@
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>my_signal</t>
+          <t>up_up</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>my_signal_3d</t>
+          <t>up_up_3d</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>my_signal_5d</t>
+          <t>up_up_5d</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>my_signal_10d</t>
+          <t>up_up_10d</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>up_up</t>
+          <t>bbw_cross</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>up_up_3d</t>
+          <t>MA_UP_d</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>up_up_5d</t>
+          <t>MA_UP_3d</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>up_up_10d</t>
+          <t>MA_UP_5d</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>bbw_cross</t>
+          <t>MA_UP_10d</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>MA_UP_3d</t>
+          <t>MA_UP_20d</t>
         </is>
       </c>
       <c r="BA1" s="1" t="inlineStr">
         <is>
-          <t>MA_UP_5d</t>
+          <t>MA_UP_30d</t>
         </is>
       </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
-          <t>MA_UP_10d</t>
+          <t>MA_UP_40d</t>
         </is>
       </c>
       <c r="BC1" s="1" t="inlineStr">
@@ -1643,62 +1643,62 @@
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
@@ -1893,11 +1893,15 @@
           <t>1112.0</t>
         </is>
       </c>
-      <c r="CQ2" t="n">
-        <v>1131.75</v>
-      </c>
-      <c r="CR2" t="n">
-        <v>1061.46</v>
+      <c r="CQ2" t="inlineStr">
+        <is>
+          <t>1131.75</t>
+        </is>
+      </c>
+      <c r="CR2" t="inlineStr">
+        <is>
+          <t>1061.46</t>
+        </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
@@ -2650,7 +2654,7 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
@@ -2665,22 +2669,22 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
@@ -2875,11 +2879,15 @@
           <t>1099.5</t>
         </is>
       </c>
-      <c r="CQ3" t="n">
-        <v>1129</v>
-      </c>
-      <c r="CR3" t="n">
-        <v>1061.36</v>
+      <c r="CQ3" t="inlineStr">
+        <is>
+          <t>1129.0</t>
+        </is>
+      </c>
+      <c r="CR3" t="inlineStr">
+        <is>
+          <t>1061.36</t>
+        </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
@@ -3632,7 +3640,7 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
@@ -3647,22 +3655,22 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
@@ -3857,11 +3865,15 @@
           <t>1095.5</t>
         </is>
       </c>
-      <c r="CQ4" t="n">
-        <v>1131.25</v>
-      </c>
-      <c r="CR4" t="n">
-        <v>1063.26</v>
+      <c r="CQ4" t="inlineStr">
+        <is>
+          <t>1131.25</t>
+        </is>
+      </c>
+      <c r="CR4" t="inlineStr">
+        <is>
+          <t>1063.26</t>
+        </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
@@ -4604,47 +4616,47 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
@@ -4839,11 +4851,15 @@
           <t>1096.5</t>
         </is>
       </c>
-      <c r="CQ5" t="n">
-        <v>1133.5</v>
-      </c>
-      <c r="CR5" t="n">
-        <v>1063.76</v>
+      <c r="CQ5" t="inlineStr">
+        <is>
+          <t>1133.5</t>
+        </is>
+      </c>
+      <c r="CR5" t="inlineStr">
+        <is>
+          <t>1063.76</t>
+        </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
@@ -5586,47 +5602,47 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
@@ -5821,11 +5837,15 @@
           <t>1111.0</t>
         </is>
       </c>
-      <c r="CQ6" t="n">
-        <v>1134.25</v>
-      </c>
-      <c r="CR6" t="n">
-        <v>1063.66</v>
+      <c r="CQ6" t="inlineStr">
+        <is>
+          <t>1134.25</t>
+        </is>
+      </c>
+      <c r="CR6" t="inlineStr">
+        <is>
+          <t>1063.66</t>
+        </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
@@ -6568,47 +6588,47 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
@@ -6803,11 +6823,15 @@
           <t>1132.0</t>
         </is>
       </c>
-      <c r="CQ7" t="n">
-        <v>1133.5</v>
-      </c>
-      <c r="CR7" t="n">
-        <v>1065.76</v>
+      <c r="CQ7" t="inlineStr">
+        <is>
+          <t>1133.5</t>
+        </is>
+      </c>
+      <c r="CR7" t="inlineStr">
+        <is>
+          <t>1065.76</t>
+        </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
@@ -7550,7 +7574,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -7560,7 +7584,7 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
@@ -7575,22 +7599,22 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
@@ -7785,11 +7809,15 @@
           <t>1146.0</t>
         </is>
       </c>
-      <c r="CQ8" t="n">
-        <v>1130.45</v>
-      </c>
-      <c r="CR8" t="n">
-        <v>1066.66</v>
+      <c r="CQ8" t="inlineStr">
+        <is>
+          <t>1130.45</t>
+        </is>
+      </c>
+      <c r="CR8" t="inlineStr">
+        <is>
+          <t>1066.66</t>
+        </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
@@ -8532,7 +8560,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -8542,7 +8570,7 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
@@ -8557,22 +8585,22 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
@@ -8767,11 +8795,15 @@
           <t>1152.5</t>
         </is>
       </c>
-      <c r="CQ9" t="n">
-        <v>1124.45</v>
-      </c>
-      <c r="CR9" t="n">
-        <v>1066.76</v>
+      <c r="CQ9" t="inlineStr">
+        <is>
+          <t>1124.45</t>
+        </is>
+      </c>
+      <c r="CR9" t="inlineStr">
+        <is>
+          <t>1066.76</t>
+        </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
@@ -9509,52 +9541,52 @@
       </c>
       <c r="AS10" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
@@ -9749,11 +9781,15 @@
           <t>1153.5</t>
         </is>
       </c>
-      <c r="CQ10" t="n">
-        <v>1118.05</v>
-      </c>
-      <c r="CR10" t="n">
-        <v>1065.76</v>
+      <c r="CQ10" t="inlineStr">
+        <is>
+          <t>1118.05</t>
+        </is>
+      </c>
+      <c r="CR10" t="inlineStr">
+        <is>
+          <t>1065.76</t>
+        </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
@@ -10496,7 +10532,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -10506,7 +10542,7 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
@@ -10516,27 +10552,27 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
@@ -10731,11 +10767,15 @@
           <t>295.75</t>
         </is>
       </c>
-      <c r="CQ11" t="n">
-        <v>295.18</v>
-      </c>
-      <c r="CR11" t="n">
-        <v>297.24</v>
+      <c r="CQ11" t="inlineStr">
+        <is>
+          <t>295.18</t>
+        </is>
+      </c>
+      <c r="CR11" t="inlineStr">
+        <is>
+          <t>297.24</t>
+        </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
@@ -11478,7 +11518,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -11488,7 +11528,7 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
@@ -11498,27 +11538,27 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
@@ -11713,11 +11753,15 @@
           <t>295.85</t>
         </is>
       </c>
-      <c r="CQ12" t="n">
-        <v>295.23</v>
-      </c>
-      <c r="CR12" t="n">
-        <v>297.51</v>
+      <c r="CQ12" t="inlineStr">
+        <is>
+          <t>295.23</t>
+        </is>
+      </c>
+      <c r="CR12" t="inlineStr">
+        <is>
+          <t>297.51</t>
+        </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
@@ -12460,7 +12504,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -12470,7 +12514,7 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
@@ -12480,27 +12524,27 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
@@ -12695,11 +12739,15 @@
           <t>296.0</t>
         </is>
       </c>
-      <c r="CQ13" t="n">
-        <v>295.23</v>
-      </c>
-      <c r="CR13" t="n">
-        <v>297.7</v>
+      <c r="CQ13" t="inlineStr">
+        <is>
+          <t>295.23</t>
+        </is>
+      </c>
+      <c r="CR13" t="inlineStr">
+        <is>
+          <t>297.7</t>
+        </is>
       </c>
       <c r="CS13" t="inlineStr">
         <is>
@@ -13442,7 +13490,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -13452,7 +13500,7 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
@@ -13467,22 +13515,22 @@
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
@@ -13677,11 +13725,15 @@
           <t>296.6</t>
         </is>
       </c>
-      <c r="CQ14" t="n">
-        <v>295.3</v>
-      </c>
-      <c r="CR14" t="n">
-        <v>297.84</v>
+      <c r="CQ14" t="inlineStr">
+        <is>
+          <t>295.3</t>
+        </is>
+      </c>
+      <c r="CR14" t="inlineStr">
+        <is>
+          <t>297.84</t>
+        </is>
       </c>
       <c r="CS14" t="inlineStr">
         <is>
@@ -14419,12 +14471,12 @@
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -14434,27 +14486,27 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
@@ -14464,7 +14516,7 @@
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
@@ -14659,11 +14711,15 @@
           <t>297.4</t>
         </is>
       </c>
-      <c r="CQ15" t="n">
-        <v>295.82</v>
-      </c>
-      <c r="CR15" t="n">
-        <v>298.07</v>
+      <c r="CQ15" t="inlineStr">
+        <is>
+          <t>295.82</t>
+        </is>
+      </c>
+      <c r="CR15" t="inlineStr">
+        <is>
+          <t>298.07</t>
+        </is>
       </c>
       <c r="CS15" t="inlineStr">
         <is>
@@ -15401,12 +15457,12 @@
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -15416,7 +15472,7 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
@@ -15426,17 +15482,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
@@ -15446,7 +15502,7 @@
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
@@ -15641,11 +15697,15 @@
           <t>297.15</t>
         </is>
       </c>
-      <c r="CQ16" t="n">
-        <v>296.3</v>
-      </c>
-      <c r="CR16" t="n">
-        <v>298.69</v>
+      <c r="CQ16" t="inlineStr">
+        <is>
+          <t>296.3</t>
+        </is>
+      </c>
+      <c r="CR16" t="inlineStr">
+        <is>
+          <t>298.69</t>
+        </is>
       </c>
       <c r="CS16" t="inlineStr">
         <is>
@@ -16378,17 +16438,17 @@
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -16398,22 +16458,22 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
@@ -16423,12 +16483,12 @@
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
@@ -16623,11 +16683,15 @@
           <t>296.85</t>
         </is>
       </c>
-      <c r="CQ17" t="n">
-        <v>296.6</v>
-      </c>
-      <c r="CR17" t="n">
-        <v>298.87</v>
+      <c r="CQ17" t="inlineStr">
+        <is>
+          <t>296.6</t>
+        </is>
+      </c>
+      <c r="CR17" t="inlineStr">
+        <is>
+          <t>298.87</t>
+        </is>
       </c>
       <c r="CS17" t="inlineStr">
         <is>
@@ -17360,17 +17424,17 @@
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -17380,22 +17444,22 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
@@ -17405,12 +17469,12 @@
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
@@ -17605,11 +17669,15 @@
           <t>296.8</t>
         </is>
       </c>
-      <c r="CQ18" t="n">
-        <v>296.73</v>
-      </c>
-      <c r="CR18" t="n">
-        <v>298.94</v>
+      <c r="CQ18" t="inlineStr">
+        <is>
+          <t>296.73</t>
+        </is>
+      </c>
+      <c r="CR18" t="inlineStr">
+        <is>
+          <t>298.94</t>
+        </is>
       </c>
       <c r="CS18" t="inlineStr">
         <is>
@@ -18337,49 +18405,49 @@
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AV19" t="inlineStr">
+      <c r="AW19" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AW19" t="inlineStr">
+      <c r="AX19" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
+      <c r="AY19" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AZ19" t="inlineStr">
         <is>
           <t>1.0</t>
@@ -18387,12 +18455,12 @@
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
@@ -18587,11 +18655,15 @@
           <t>296.65</t>
         </is>
       </c>
-      <c r="CQ19" t="n">
-        <v>296.4</v>
-      </c>
-      <c r="CR19" t="n">
-        <v>299.06</v>
+      <c r="CQ19" t="inlineStr">
+        <is>
+          <t>296.4</t>
+        </is>
+      </c>
+      <c r="CR19" t="inlineStr">
+        <is>
+          <t>299.06</t>
+        </is>
       </c>
       <c r="CS19" t="inlineStr">
         <is>
@@ -19344,7 +19416,7 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
@@ -19359,7 +19431,7 @@
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
@@ -19569,11 +19641,15 @@
           <t>427.15</t>
         </is>
       </c>
-      <c r="CQ20" t="n">
-        <v>436.7</v>
-      </c>
-      <c r="CR20" t="n">
-        <v>470.83</v>
+      <c r="CQ20" t="inlineStr">
+        <is>
+          <t>436.7</t>
+        </is>
+      </c>
+      <c r="CR20" t="inlineStr">
+        <is>
+          <t>470.83</t>
+        </is>
       </c>
       <c r="CS20" t="inlineStr">
         <is>
@@ -20326,7 +20402,7 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
@@ -20341,7 +20417,7 @@
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
@@ -20551,11 +20627,15 @@
           <t>427.1</t>
         </is>
       </c>
-      <c r="CQ21" t="n">
-        <v>439.5</v>
-      </c>
-      <c r="CR21" t="n">
-        <v>474.14</v>
+      <c r="CQ21" t="inlineStr">
+        <is>
+          <t>439.5</t>
+        </is>
+      </c>
+      <c r="CR21" t="inlineStr">
+        <is>
+          <t>474.14</t>
+        </is>
       </c>
       <c r="CS21" t="inlineStr">
         <is>
@@ -21308,7 +21388,7 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
@@ -21323,7 +21403,7 @@
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
@@ -21533,11 +21613,15 @@
           <t>427.15</t>
         </is>
       </c>
-      <c r="CQ22" t="n">
-        <v>441.9</v>
-      </c>
-      <c r="CR22" t="n">
-        <v>477.31</v>
+      <c r="CQ22" t="inlineStr">
+        <is>
+          <t>441.9</t>
+        </is>
+      </c>
+      <c r="CR22" t="inlineStr">
+        <is>
+          <t>477.31</t>
+        </is>
       </c>
       <c r="CS22" t="inlineStr">
         <is>
@@ -22290,7 +22374,7 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
@@ -22305,7 +22389,7 @@
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
@@ -22515,11 +22599,15 @@
           <t>427.5</t>
         </is>
       </c>
-      <c r="CQ23" t="n">
-        <v>443.58</v>
-      </c>
-      <c r="CR23" t="n">
-        <v>480.06</v>
+      <c r="CQ23" t="inlineStr">
+        <is>
+          <t>443.58</t>
+        </is>
+      </c>
+      <c r="CR23" t="inlineStr">
+        <is>
+          <t>480.06</t>
+        </is>
       </c>
       <c r="CS23" t="inlineStr">
         <is>
@@ -23272,7 +23360,7 @@
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
@@ -23287,7 +23375,7 @@
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ24" t="inlineStr">
@@ -23497,11 +23585,15 @@
           <t>427.9</t>
         </is>
       </c>
-      <c r="CQ24" t="n">
-        <v>445.48</v>
-      </c>
-      <c r="CR24" t="n">
-        <v>482.68</v>
+      <c r="CQ24" t="inlineStr">
+        <is>
+          <t>445.48</t>
+        </is>
+      </c>
+      <c r="CR24" t="inlineStr">
+        <is>
+          <t>482.68</t>
+        </is>
       </c>
       <c r="CS24" t="inlineStr">
         <is>
@@ -24254,7 +24346,7 @@
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
@@ -24269,7 +24361,7 @@
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ25" t="inlineStr">
@@ -24479,11 +24571,15 @@
           <t>429.2</t>
         </is>
       </c>
-      <c r="CQ25" t="n">
-        <v>447.45</v>
-      </c>
-      <c r="CR25" t="n">
-        <v>486.16</v>
+      <c r="CQ25" t="inlineStr">
+        <is>
+          <t>447.45</t>
+        </is>
+      </c>
+      <c r="CR25" t="inlineStr">
+        <is>
+          <t>486.16</t>
+        </is>
       </c>
       <c r="CS25" t="inlineStr">
         <is>
@@ -25236,7 +25332,7 @@
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
@@ -25251,7 +25347,7 @@
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ26" t="inlineStr">
@@ -25461,11 +25557,15 @@
           <t>431.65</t>
         </is>
       </c>
-      <c r="CQ26" t="n">
-        <v>449.08</v>
-      </c>
-      <c r="CR26" t="n">
-        <v>489.61</v>
+      <c r="CQ26" t="inlineStr">
+        <is>
+          <t>449.08</t>
+        </is>
+      </c>
+      <c r="CR26" t="inlineStr">
+        <is>
+          <t>489.61</t>
+        </is>
       </c>
       <c r="CS26" t="inlineStr">
         <is>
@@ -26218,7 +26318,7 @@
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
@@ -26233,7 +26333,7 @@
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
@@ -26443,11 +26543,15 @@
           <t>435.05</t>
         </is>
       </c>
-      <c r="CQ27" t="n">
-        <v>450.52</v>
-      </c>
-      <c r="CR27" t="n">
-        <v>492.97</v>
+      <c r="CQ27" t="inlineStr">
+        <is>
+          <t>450.52</t>
+        </is>
+      </c>
+      <c r="CR27" t="inlineStr">
+        <is>
+          <t>492.97</t>
+        </is>
       </c>
       <c r="CS27" t="inlineStr">
         <is>
@@ -27200,7 +27304,7 @@
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
@@ -27215,7 +27319,7 @@
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ28" t="inlineStr">
@@ -27425,11 +27529,15 @@
           <t>437.85</t>
         </is>
       </c>
-      <c r="CQ28" t="n">
-        <v>452.38</v>
-      </c>
-      <c r="CR28" t="n">
-        <v>496.43</v>
+      <c r="CQ28" t="inlineStr">
+        <is>
+          <t>452.38</t>
+        </is>
+      </c>
+      <c r="CR28" t="inlineStr">
+        <is>
+          <t>496.43</t>
+        </is>
       </c>
       <c r="CS28" t="inlineStr">
         <is>
@@ -28182,7 +28290,7 @@
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
@@ -28197,7 +28305,7 @@
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ29" t="inlineStr">
@@ -28207,12 +28315,12 @@
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
@@ -28407,11 +28515,15 @@
           <t>129.2</t>
         </is>
       </c>
-      <c r="CQ29" t="n">
-        <v>131.22</v>
-      </c>
-      <c r="CR29" t="n">
-        <v>140.14</v>
+      <c r="CQ29" t="inlineStr">
+        <is>
+          <t>131.22</t>
+        </is>
+      </c>
+      <c r="CR29" t="inlineStr">
+        <is>
+          <t>140.14</t>
+        </is>
       </c>
       <c r="CS29" t="inlineStr">
         <is>
@@ -29164,7 +29276,7 @@
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
@@ -29179,7 +29291,7 @@
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ30" t="inlineStr">
@@ -29189,12 +29301,12 @@
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
@@ -29389,11 +29501,15 @@
           <t>129.3</t>
         </is>
       </c>
-      <c r="CQ30" t="n">
-        <v>132.02</v>
-      </c>
-      <c r="CR30" t="n">
-        <v>140.35</v>
+      <c r="CQ30" t="inlineStr">
+        <is>
+          <t>132.02</t>
+        </is>
+      </c>
+      <c r="CR30" t="inlineStr">
+        <is>
+          <t>140.35</t>
+        </is>
       </c>
       <c r="CS30" t="inlineStr">
         <is>
@@ -30146,7 +30262,7 @@
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
@@ -30161,7 +30277,7 @@
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ31" t="inlineStr">
@@ -30171,12 +30287,12 @@
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
@@ -30371,11 +30487,15 @@
           <t>129.0</t>
         </is>
       </c>
-      <c r="CQ31" t="n">
-        <v>132.82</v>
-      </c>
-      <c r="CR31" t="n">
-        <v>140.56</v>
+      <c r="CQ31" t="inlineStr">
+        <is>
+          <t>132.82</t>
+        </is>
+      </c>
+      <c r="CR31" t="inlineStr">
+        <is>
+          <t>140.56</t>
+        </is>
       </c>
       <c r="CS31" t="inlineStr">
         <is>
@@ -31128,7 +31248,7 @@
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
@@ -31143,7 +31263,7 @@
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ32" t="inlineStr">
@@ -31153,12 +31273,12 @@
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
@@ -31353,11 +31473,15 @@
           <t>128.8</t>
         </is>
       </c>
-      <c r="CQ32" t="n">
-        <v>133.62</v>
-      </c>
-      <c r="CR32" t="n">
-        <v>140.68</v>
+      <c r="CQ32" t="inlineStr">
+        <is>
+          <t>133.62</t>
+        </is>
+      </c>
+      <c r="CR32" t="inlineStr">
+        <is>
+          <t>140.68</t>
+        </is>
       </c>
       <c r="CS32" t="inlineStr">
         <is>
@@ -32110,7 +32234,7 @@
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
@@ -32125,7 +32249,7 @@
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ33" t="inlineStr">
@@ -32135,12 +32259,12 @@
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
@@ -32335,11 +32459,15 @@
           <t>128.75</t>
         </is>
       </c>
-      <c r="CQ33" t="n">
-        <v>134.48</v>
-      </c>
-      <c r="CR33" t="n">
-        <v>140.93</v>
+      <c r="CQ33" t="inlineStr">
+        <is>
+          <t>134.48</t>
+        </is>
+      </c>
+      <c r="CR33" t="inlineStr">
+        <is>
+          <t>140.93</t>
+        </is>
       </c>
       <c r="CS33" t="inlineStr">
         <is>
@@ -33092,7 +33220,7 @@
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
@@ -33107,7 +33235,7 @@
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
@@ -33117,12 +33245,12 @@
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
@@ -33317,11 +33445,15 @@
           <t>129.0</t>
         </is>
       </c>
-      <c r="CQ34" t="n">
-        <v>135.48</v>
-      </c>
-      <c r="CR34" t="n">
-        <v>141.32</v>
+      <c r="CQ34" t="inlineStr">
+        <is>
+          <t>135.48</t>
+        </is>
+      </c>
+      <c r="CR34" t="inlineStr">
+        <is>
+          <t>141.32</t>
+        </is>
       </c>
       <c r="CS34" t="inlineStr">
         <is>
@@ -34074,7 +34206,7 @@
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
@@ -34089,7 +34221,7 @@
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
@@ -34099,12 +34231,12 @@
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BC35" t="inlineStr">
@@ -34299,11 +34431,15 @@
           <t>129.55</t>
         </is>
       </c>
-      <c r="CQ35" t="n">
-        <v>136.4</v>
-      </c>
-      <c r="CR35" t="n">
-        <v>141.64</v>
+      <c r="CQ35" t="inlineStr">
+        <is>
+          <t>136.4</t>
+        </is>
+      </c>
+      <c r="CR35" t="inlineStr">
+        <is>
+          <t>141.64</t>
+        </is>
       </c>
       <c r="CS35" t="inlineStr">
         <is>
@@ -35056,7 +35192,7 @@
       </c>
       <c r="AV36" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW36" t="inlineStr">
@@ -35071,7 +35207,7 @@
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
@@ -35081,12 +35217,12 @@
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BC36" t="inlineStr">
@@ -35281,11 +35417,15 @@
           <t>130.1</t>
         </is>
       </c>
-      <c r="CQ36" t="n">
-        <v>137.15</v>
-      </c>
-      <c r="CR36" t="n">
-        <v>141.89</v>
+      <c r="CQ36" t="inlineStr">
+        <is>
+          <t>137.15</t>
+        </is>
+      </c>
+      <c r="CR36" t="inlineStr">
+        <is>
+          <t>141.89</t>
+        </is>
       </c>
       <c r="CS36" t="inlineStr">
         <is>
@@ -36038,7 +36178,7 @@
       </c>
       <c r="AV37" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW37" t="inlineStr">
@@ -36053,7 +36193,7 @@
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr">
@@ -36063,12 +36203,12 @@
       </c>
       <c r="BA37" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB37" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BC37" t="inlineStr">
@@ -36263,11 +36403,15 @@
           <t>131.1</t>
         </is>
       </c>
-      <c r="CQ37" t="n">
-        <v>137.82</v>
-      </c>
-      <c r="CR37" t="n">
-        <v>142.21</v>
+      <c r="CQ37" t="inlineStr">
+        <is>
+          <t>137.82</t>
+        </is>
+      </c>
+      <c r="CR37" t="inlineStr">
+        <is>
+          <t>142.21</t>
+        </is>
       </c>
       <c r="CS37" t="inlineStr">
         <is>
@@ -37020,7 +37164,7 @@
       </c>
       <c r="AV38" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW38" t="inlineStr">
@@ -37035,7 +37179,7 @@
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ38" t="inlineStr">
@@ -37050,7 +37194,7 @@
       </c>
       <c r="BB38" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BC38" t="inlineStr">
@@ -37245,11 +37389,15 @@
           <t>332.25</t>
         </is>
       </c>
-      <c r="CQ38" t="n">
-        <v>341.05</v>
-      </c>
-      <c r="CR38" t="n">
-        <v>345.19</v>
+      <c r="CQ38" t="inlineStr">
+        <is>
+          <t>341.05</t>
+        </is>
+      </c>
+      <c r="CR38" t="inlineStr">
+        <is>
+          <t>345.19</t>
+        </is>
       </c>
       <c r="CS38" t="inlineStr">
         <is>
@@ -38002,7 +38150,7 @@
       </c>
       <c r="AV39" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW39" t="inlineStr">
@@ -38017,7 +38165,7 @@
       </c>
       <c r="AY39" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ39" t="inlineStr">
@@ -38032,7 +38180,7 @@
       </c>
       <c r="BB39" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BC39" t="inlineStr">
@@ -38227,11 +38375,15 @@
           <t>332.15</t>
         </is>
       </c>
-      <c r="CQ39" t="n">
-        <v>342.02</v>
-      </c>
-      <c r="CR39" t="n">
-        <v>344.95</v>
+      <c r="CQ39" t="inlineStr">
+        <is>
+          <t>342.02</t>
+        </is>
+      </c>
+      <c r="CR39" t="inlineStr">
+        <is>
+          <t>344.95</t>
+        </is>
       </c>
       <c r="CS39" t="inlineStr">
         <is>
@@ -38984,7 +39136,7 @@
       </c>
       <c r="AV40" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW40" t="inlineStr">
@@ -38999,7 +39151,7 @@
       </c>
       <c r="AY40" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ40" t="inlineStr">
@@ -39014,7 +39166,7 @@
       </c>
       <c r="BB40" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BC40" t="inlineStr">
@@ -39209,11 +39361,15 @@
           <t>331.55</t>
         </is>
       </c>
-      <c r="CQ40" t="n">
-        <v>343.22</v>
-      </c>
-      <c r="CR40" t="n">
-        <v>344.35</v>
+      <c r="CQ40" t="inlineStr">
+        <is>
+          <t>343.22</t>
+        </is>
+      </c>
+      <c r="CR40" t="inlineStr">
+        <is>
+          <t>344.35</t>
+        </is>
       </c>
       <c r="CS40" t="inlineStr">
         <is>
@@ -39966,7 +40122,7 @@
       </c>
       <c r="AV41" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW41" t="inlineStr">
@@ -39981,7 +40137,7 @@
       </c>
       <c r="AY41" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ41" t="inlineStr">
@@ -39996,7 +40152,7 @@
       </c>
       <c r="BB41" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BC41" t="inlineStr">
@@ -40191,11 +40347,15 @@
           <t>330.4</t>
         </is>
       </c>
-      <c r="CQ41" t="n">
-        <v>343.98</v>
-      </c>
-      <c r="CR41" t="n">
-        <v>343.65</v>
+      <c r="CQ41" t="inlineStr">
+        <is>
+          <t>343.98</t>
+        </is>
+      </c>
+      <c r="CR41" t="inlineStr">
+        <is>
+          <t>343.65</t>
+        </is>
       </c>
       <c r="CS41" t="inlineStr">
         <is>
@@ -40948,7 +41108,7 @@
       </c>
       <c r="AV42" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW42" t="inlineStr">
@@ -40963,7 +41123,7 @@
       </c>
       <c r="AY42" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ42" t="inlineStr">
@@ -40978,7 +41138,7 @@
       </c>
       <c r="BB42" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BC42" t="inlineStr">
@@ -41173,11 +41333,15 @@
           <t>332.75</t>
         </is>
       </c>
-      <c r="CQ42" t="n">
-        <v>344.9</v>
-      </c>
-      <c r="CR42" t="n">
-        <v>343.06</v>
+      <c r="CQ42" t="inlineStr">
+        <is>
+          <t>344.9</t>
+        </is>
+      </c>
+      <c r="CR42" t="inlineStr">
+        <is>
+          <t>343.06</t>
+        </is>
       </c>
       <c r="CS42" t="inlineStr">
         <is>
@@ -41930,7 +42094,7 @@
       </c>
       <c r="AV43" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW43" t="inlineStr">
@@ -41945,7 +42109,7 @@
       </c>
       <c r="AY43" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ43" t="inlineStr">
@@ -41955,12 +42119,12 @@
       </c>
       <c r="BA43" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BB43" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BC43" t="inlineStr">
@@ -42155,11 +42319,15 @@
           <t>336.5</t>
         </is>
       </c>
-      <c r="CQ43" t="n">
-        <v>346.6</v>
-      </c>
-      <c r="CR43" t="n">
-        <v>343.19</v>
+      <c r="CQ43" t="inlineStr">
+        <is>
+          <t>346.6</t>
+        </is>
+      </c>
+      <c r="CR43" t="inlineStr">
+        <is>
+          <t>343.19</t>
+        </is>
       </c>
       <c r="CS43" t="inlineStr">
         <is>
@@ -42912,7 +43080,7 @@
       </c>
       <c r="AV44" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW44" t="inlineStr">
@@ -42927,7 +43095,7 @@
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ44" t="inlineStr">
@@ -42937,12 +43105,12 @@
       </c>
       <c r="BA44" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BB44" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BC44" t="inlineStr">
@@ -43137,11 +43305,15 @@
           <t>341.2</t>
         </is>
       </c>
-      <c r="CQ44" t="n">
-        <v>348.08</v>
-      </c>
-      <c r="CR44" t="n">
-        <v>343.15</v>
+      <c r="CQ44" t="inlineStr">
+        <is>
+          <t>348.08</t>
+        </is>
+      </c>
+      <c r="CR44" t="inlineStr">
+        <is>
+          <t>343.15</t>
+        </is>
       </c>
       <c r="CS44" t="inlineStr">
         <is>
@@ -43894,7 +44066,7 @@
       </c>
       <c r="AV45" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW45" t="inlineStr">
@@ -43909,7 +44081,7 @@
       </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ45" t="inlineStr">
@@ -43919,12 +44091,12 @@
       </c>
       <c r="BA45" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BB45" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BC45" t="inlineStr">
@@ -44119,11 +44291,15 @@
           <t>343.1</t>
         </is>
       </c>
-      <c r="CQ45" t="n">
-        <v>348.8</v>
-      </c>
-      <c r="CR45" t="n">
-        <v>342.87</v>
+      <c r="CQ45" t="inlineStr">
+        <is>
+          <t>348.8</t>
+        </is>
+      </c>
+      <c r="CR45" t="inlineStr">
+        <is>
+          <t>342.87</t>
+        </is>
       </c>
       <c r="CS45" t="inlineStr">
         <is>
@@ -44876,7 +45052,7 @@
       </c>
       <c r="AV46" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW46" t="inlineStr">
@@ -44891,7 +45067,7 @@
       </c>
       <c r="AY46" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ46" t="inlineStr">
@@ -44901,12 +45077,12 @@
       </c>
       <c r="BA46" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BB46" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BC46" t="inlineStr">
@@ -45101,11 +45277,15 @@
           <t>346.15</t>
         </is>
       </c>
-      <c r="CQ46" t="n">
-        <v>349.28</v>
-      </c>
-      <c r="CR46" t="n">
-        <v>342.83</v>
+      <c r="CQ46" t="inlineStr">
+        <is>
+          <t>349.28</t>
+        </is>
+      </c>
+      <c r="CR46" t="inlineStr">
+        <is>
+          <t>342.83</t>
+        </is>
       </c>
       <c r="CS46" t="inlineStr">
         <is>
